--- a/verification_forms/042_driver_s_license_verification_form--verification_forms.xlsx
+++ b/verification_forms/042_driver_s_license_verification_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>west_virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wisconsin</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
@@ -1864,29 +1864,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>wyoming</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>country_of_issue_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>united_states</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -1932,27 +1932,10 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>country_of_issue_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
